--- a/Shelter_Scheduled_Checkouts_2025-2027.xlsx
+++ b/Shelter_Scheduled_Checkouts_2025-2027.xlsx
@@ -8254,11 +8254,11 @@
         <v/>
       </c>
       <c r="I5" s="19">
-        <f>_xlfn.MINIFS('All Shelter Checkouts'!$B$5:$B$68,'All Shelter Checkouts'!$A$5:$A$68,$A5)</f>
+        <f>MIN('All Shelter Checkouts'!$B$5:$B$36)</f>
         <v/>
       </c>
       <c r="J5" s="19">
-        <f>_xlfn.MAXIFS('All Shelter Checkouts'!$B$5:$B$68,'All Shelter Checkouts'!$A$5:$A$68,$A5)</f>
+        <f>MAX('All Shelter Checkouts'!$B$5:$B$36)</f>
         <v/>
       </c>
       <c r="K5" s="20">
@@ -8302,11 +8302,11 @@
         <v/>
       </c>
       <c r="I6" s="19">
-        <f>_xlfn.MINIFS('All Shelter Checkouts'!$B$5:$B$68,'All Shelter Checkouts'!$A$5:$A$68,$A6)</f>
+        <f>MIN('All Shelter Checkouts'!$B$37:$B$41)</f>
         <v/>
       </c>
       <c r="J6" s="19">
-        <f>_xlfn.MAXIFS('All Shelter Checkouts'!$B$5:$B$68,'All Shelter Checkouts'!$A$5:$A$68,$A6)</f>
+        <f>MAX('All Shelter Checkouts'!$B$37:$B$41)</f>
         <v/>
       </c>
       <c r="K6" s="20">
@@ -8350,11 +8350,11 @@
         <v/>
       </c>
       <c r="I7" s="19">
-        <f>_xlfn.MINIFS('All Shelter Checkouts'!$B$5:$B$68,'All Shelter Checkouts'!$A$5:$A$68,$A7)</f>
+        <f>MIN('All Shelter Checkouts'!$B$42:$B$57)</f>
         <v/>
       </c>
       <c r="J7" s="19">
-        <f>_xlfn.MAXIFS('All Shelter Checkouts'!$B$5:$B$68,'All Shelter Checkouts'!$A$5:$A$68,$A7)</f>
+        <f>MAX('All Shelter Checkouts'!$B$42:$B$57)</f>
         <v/>
       </c>
       <c r="K7" s="20">
@@ -8398,11 +8398,11 @@
         <v/>
       </c>
       <c r="I8" s="19">
-        <f>_xlfn.MINIFS('All Shelter Checkouts'!$B$5:$B$68,'All Shelter Checkouts'!$A$5:$A$68,$A8)</f>
+        <f>MIN('All Shelter Checkouts'!$B$58:$B$66)</f>
         <v/>
       </c>
       <c r="J8" s="19">
-        <f>_xlfn.MAXIFS('All Shelter Checkouts'!$B$5:$B$68,'All Shelter Checkouts'!$A$5:$A$68,$A8)</f>
+        <f>MAX('All Shelter Checkouts'!$B$58:$B$66)</f>
         <v/>
       </c>
       <c r="K8" s="20">
@@ -8446,11 +8446,11 @@
         <v/>
       </c>
       <c r="I9" s="19">
-        <f>_xlfn.MINIFS('All Shelter Checkouts'!$B$5:$B$68,'All Shelter Checkouts'!$A$5:$A$68,$A9)</f>
+        <f>MIN('All Shelter Checkouts'!$B$67:$B$68)</f>
         <v/>
       </c>
       <c r="J9" s="19">
-        <f>_xlfn.MAXIFS('All Shelter Checkouts'!$B$5:$B$68,'All Shelter Checkouts'!$A$5:$A$68,$A9)</f>
+        <f>MAX('All Shelter Checkouts'!$B$67:$B$68)</f>
         <v/>
       </c>
       <c r="K9" s="20">
